--- a/data/raw/GLNPO 2024 Spring/Huron/D20/Zoops/HU 15M D20 QA Spring 2024 24GH00Q74 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Huron/D20/Zoops/HU 15M D20 QA Spring 2024 24GH00Q74 Zoop.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gl Lab User\Desktop\GLNPO Spring\GLNPO Spring 2024\Huron\D20\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Huron\D20\Zoops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8C94F13-927D-4160-A5B4-61CA3FE5923A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026E521E-C7EF-41E4-AC46-69A96E9BAA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{FC00CDBE-2038-4C6B-B2B7-5E6A81666B65}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FC00CDBE-2038-4C6B-B2B7-5E6A81666B65}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Y$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$166</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1146" r:id="rId2"/>
+    <pivotCache cacheId="48" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -349,14 +349,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -3602,7 +3601,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1B3A1F26-0C23-47E3-BB26-3A939CC60CB9}" name="PivotTable2" cacheId="1146" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1B3A1F26-0C23-47E3-BB26-3A939CC60CB9}" name="PivotTable2" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T3:Y17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -4043,18 +4042,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE29D7E-7E97-4C4D-9C3D-146218A22BD7}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y166"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="20" max="20" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.42578125" customWidth="1"/>
-    <col min="23" max="23" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.44140625" customWidth="1"/>
+    <col min="23" max="23" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4110,7 +4111,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -4163,7 +4164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -4222,7 +4223,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -4293,7 +4294,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4337,10 +4338,10 @@
         <v>29</v>
       </c>
       <c r="O5">
-        <v>0.46200000000000002</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="P5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -4348,17 +4349,14 @@
       <c r="T5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="U5" s="4">
+      <c r="U5">
         <v>41</v>
       </c>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4">
+      <c r="Y5">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -4413,19 +4411,17 @@
       <c r="T6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="U6" s="4">
+      <c r="U6">
         <v>0</v>
       </c>
-      <c r="V6" s="4">
-        <v>1</v>
-      </c>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -4480,17 +4476,14 @@
       <c r="T7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="U7" s="4">
+      <c r="U7">
         <v>31</v>
       </c>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4">
+      <c r="Y7">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -4545,17 +4538,14 @@
       <c r="T8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="U8" s="4">
+      <c r="U8">
         <v>28</v>
       </c>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4">
+      <c r="Y8">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -4610,17 +4600,14 @@
       <c r="T9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="U9" s="4">
+      <c r="U9">
         <v>76</v>
       </c>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4">
+      <c r="Y9">
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -4675,17 +4662,14 @@
       <c r="T10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="U10" s="4">
+      <c r="U10">
         <v>81</v>
       </c>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4">
+      <c r="Y10">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -4740,17 +4724,14 @@
       <c r="T11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="U11" s="4">
+      <c r="U11">
         <v>61</v>
       </c>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4">
+      <c r="Y11">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -4805,21 +4786,20 @@
       <c r="T12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="U12" s="4">
+      <c r="U12">
         <v>0</v>
       </c>
-      <c r="V12" s="4">
+      <c r="V12">
         <v>7</v>
       </c>
-      <c r="W12" s="4">
+      <c r="W12">
         <v>7</v>
       </c>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4">
+      <c r="Y12">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -4874,17 +4854,14 @@
       <c r="T13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4">
+      <c r="X13">
         <v>2</v>
       </c>
-      <c r="Y13" s="4">
+      <c r="Y13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -4939,19 +4916,17 @@
       <c r="T14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="U14" s="4">
+      <c r="U14">
         <v>0</v>
       </c>
-      <c r="V14" s="4">
-        <v>1</v>
-      </c>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="Y14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -5006,19 +4981,17 @@
       <c r="T15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="U15" s="4">
+      <c r="U15">
         <v>2</v>
       </c>
-      <c r="V15" s="4">
+      <c r="V15">
         <v>8</v>
       </c>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4">
+      <c r="Y15">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -5073,19 +5046,17 @@
       <c r="T16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="U16" s="4">
+      <c r="U16">
         <v>0</v>
       </c>
-      <c r="V16" s="4">
-        <v>1</v>
-      </c>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -5140,23 +5111,23 @@
       <c r="T17" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="U17" s="4">
+      <c r="U17">
         <v>320</v>
       </c>
-      <c r="V17" s="4">
-        <v>18</v>
-      </c>
-      <c r="W17" s="4">
+      <c r="V17">
+        <v>18</v>
+      </c>
+      <c r="W17">
         <v>7</v>
       </c>
-      <c r="X17" s="4">
+      <c r="X17">
         <v>2</v>
       </c>
-      <c r="Y17" s="4">
+      <c r="Y17">
         <v>347</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -5209,7 +5180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -5262,7 +5233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -5314,13 +5285,13 @@
       <c r="Q20">
         <v>1</v>
       </c>
-      <c r="T20" s="5" t="s">
+      <c r="T20" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="U20" s="6"/>
-      <c r="V20" s="6"/>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+    </row>
+    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -5372,17 +5343,17 @@
       <c r="Q21">
         <v>1</v>
       </c>
-      <c r="T21" s="5" t="s">
+      <c r="T21" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="U21" s="6" t="s">
+      <c r="U21" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="V21" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -5434,15 +5405,15 @@
       <c r="Q22">
         <v>1</v>
       </c>
-      <c r="T22" s="5"/>
-      <c r="U22" s="6" t="s">
+      <c r="T22" s="4"/>
+      <c r="U22" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="V22" s="7">
+      <c r="V22" s="6">
         <v>0.996</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -5494,17 +5465,17 @@
       <c r="Q23">
         <v>1</v>
       </c>
-      <c r="T23" s="5" t="s">
+      <c r="T23" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="U23" s="6" t="s">
+      <c r="U23" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="V23" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V23" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -5556,15 +5527,15 @@
       <c r="Q24">
         <v>1</v>
       </c>
-      <c r="T24" s="5"/>
-      <c r="U24" s="6" t="s">
+      <c r="T24" s="4"/>
+      <c r="U24" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="V24" s="6">
+      <c r="V24" s="5">
         <v>0.995</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -5616,15 +5587,15 @@
       <c r="Q25">
         <v>1</v>
       </c>
-      <c r="T25" s="5" t="s">
+      <c r="T25" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="U25" s="6" t="s">
+      <c r="U25" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="V25" s="6"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V25" s="5"/>
+    </row>
+    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -5676,15 +5647,15 @@
       <c r="Q26">
         <v>1</v>
       </c>
-      <c r="T26" s="5" t="s">
+      <c r="T26" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="U26" s="6" t="s">
+      <c r="U26" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V26" s="6"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V26" s="5"/>
+    </row>
+    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -5736,12 +5707,12 @@
       <c r="Q27">
         <v>1</v>
       </c>
-      <c r="T27" s="5" t="s">
+      <c r="T27" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="U27" s="6"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="U27" s="5"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -5794,7 +5765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -5847,7 +5818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -5900,7 +5871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -5953,7 +5924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -6006,7 +5977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -6059,7 +6030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -6112,7 +6083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -6165,7 +6136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -6218,7 +6189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -6271,7 +6242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -6324,7 +6295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -6377,7 +6348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -6430,7 +6401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -6483,7 +6454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -6536,7 +6507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -6589,7 +6560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -6642,7 +6613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -6695,7 +6666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -6748,7 +6719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -6801,7 +6772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -6854,7 +6825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -6907,7 +6878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -6960,7 +6931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -7013,7 +6984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -7066,7 +7037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -7119,7 +7090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -7166,7 +7137,7 @@
         <v>35</v>
       </c>
       <c r="P54" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q54">
         <v>1</v>
@@ -7175,7 +7146,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -7228,7 +7199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -7281,7 +7252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -7334,7 +7305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -7387,7 +7358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -7440,7 +7411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -7493,7 +7464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -7546,7 +7517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -7599,7 +7570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -7652,7 +7623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -7705,7 +7676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -7758,7 +7729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -7811,7 +7782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -7864,7 +7835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -7917,7 +7888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -7970,7 +7941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -8023,7 +7994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -8076,7 +8047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -8129,7 +8100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -8182,7 +8153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -8235,7 +8206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -8288,7 +8259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -8341,7 +8312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -8394,7 +8365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -8447,7 +8418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -8500,7 +8471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -8553,7 +8524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -8606,7 +8577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -8659,7 +8630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -8712,7 +8683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -8765,7 +8736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -8818,7 +8789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -8871,7 +8842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -8924,7 +8895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -8977,7 +8948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -9030,7 +9001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -9083,7 +9054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -9136,7 +9107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -9189,7 +9160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -9242,7 +9213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -9295,7 +9266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -9348,7 +9319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -9401,7 +9372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -9454,7 +9425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -9507,7 +9478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -9560,7 +9531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -9613,7 +9584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -9666,7 +9637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -9719,7 +9690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -9772,7 +9743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -9825,7 +9796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -9878,7 +9849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -9931,7 +9902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -9984,7 +9955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -10037,7 +10008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -10090,7 +10061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -10143,7 +10114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -10196,7 +10167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -10249,7 +10220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -10302,7 +10273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -10355,7 +10326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -10408,7 +10379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -10461,7 +10432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -10514,7 +10485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -10567,7 +10538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -10620,7 +10591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -10673,7 +10644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -10726,7 +10697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -10779,7 +10750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -10832,7 +10803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -10885,7 +10856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -10938,7 +10909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -10991,7 +10962,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -11044,7 +11015,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -11097,7 +11068,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -11150,7 +11121,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -11197,13 +11168,13 @@
         <v>35</v>
       </c>
       <c r="P130" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q130">
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -11250,13 +11221,13 @@
         <v>35</v>
       </c>
       <c r="P131" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="Q131">
         <v>14</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -11309,7 +11280,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -11362,7 +11333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -11415,7 +11386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -11468,7 +11439,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -11521,7 +11492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -11574,7 +11545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -11627,7 +11598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -11680,7 +11651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -11733,7 +11704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -11786,7 +11757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -11839,7 +11810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -11895,7 +11866,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -11948,7 +11919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -12001,7 +11972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -12054,7 +12025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -12107,7 +12078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -12160,7 +12131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -12213,7 +12184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -12266,7 +12237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -12319,7 +12290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -12372,7 +12343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -12425,7 +12396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -12478,7 +12449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -12531,7 +12502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -12584,7 +12555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -12637,7 +12608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -12690,7 +12661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -12743,7 +12714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -12796,7 +12767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -12849,7 +12820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -12902,7 +12873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -12955,7 +12926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -13008,7 +12979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -13061,7 +13032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -13115,7 +13086,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y166" xr:uid="{1CE29D7E-7E97-4C4D-9C3D-146218A22BD7}"/>
+  <autoFilter ref="A1:R166" xr:uid="{1CE29D7E-7E97-4C4D-9C3D-146218A22BD7}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Leptodiaptomus ashlandi"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>